--- a/Result/checksun_type/電容器材料(如電蝕／化成鋁箔、介面瓷粉).xlsx
+++ b/Result/checksun_type/電容器材料(如電蝕／化成鋁箔、介面瓷粉).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>46.15</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>46.74</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>43.73</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>46.74</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>43.73</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>52144.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>144223.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>144223.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>263061.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>271789.26</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>271789.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-52351.73424423317</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>52144</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>52144.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>46.2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>47.06</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>43.54</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>43.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>112104.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>169510.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>169510.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>312401.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>271468.38</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>271468.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-44932.56014636956</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>112104</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>112104.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>46.26000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>43.38</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>43.38</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>154066.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>183150.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>183150.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>324557.4</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>269911.18</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>269911.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-39153.29142990836</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>154066</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>154066.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>46.1</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>47.88</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>43.2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>257737.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>201385.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>201385.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>321190.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>268146.0</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>268146</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-33994.78999818134</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>257737</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>257737.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>46.59</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>48.01</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>43.06</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>43.06</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>145065.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>269679.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>269679.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>304409.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>263522.92</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>263522.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-36519.00973863632</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>145065</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>145065.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>47.31</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>47.92</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>42.93</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>42.93</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>178579.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>381900.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>381900.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>302590.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>261160.12</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>261160.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-26748.78759147774</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>178579</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>178579.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>47.91</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>47.82</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>42.8</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>42.8</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>180305.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>455292.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>455292.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>297710.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>258048.18</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>258048.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-15426.79925298417</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>180305</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>180305.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>47.92</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>47.78</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>42.68</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>42.68</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>245241.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>465964.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>465964.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>300859.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>254747.64</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>254747.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>1113.498346756038</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>245241</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>245241.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>47.41</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>47.52</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>42.54</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>42.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>599206.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>440995.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>440995.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>299401.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>250416.8</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>250416.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>17745.29854828649</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>599206</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>599206.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>46.73999999999999</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>47.02</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>42.35</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>42.35</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>706170.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>339139.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>339139.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>261996.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>239519.48</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>239519.48</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>2946.431030891195</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>706170</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>706170.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>46.16</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>42.17</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>46.43</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>42.17</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>545541.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>223280.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>223280</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>231536.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>226428.56</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>226428.56</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-29760.4665307767</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>545541</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>545541.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>67.26</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>64.05</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>56.78</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>56.78</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>638643.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>2407911.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>2407911.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>2702992.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1324655.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1324655</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>21217.33786260104</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>638643</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>638643.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>68.2</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>63.94</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>56.29</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>56.29</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>1336332.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>2902642.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>2902642.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>2848361.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1312295.78</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1312295.78</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>183468.6577617624</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>1336332</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1336332.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>68.17999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>63.86</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>55.79</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>63.86</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>55.79</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2057569.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>3130392.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>3130392.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2791581.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1285932.64</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1285932.64</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>333951.4126976444</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2057569</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2057569.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>67.2</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>63.64</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>55.22</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>55.22</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>4654722.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3076584.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>3076584.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>2618461.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1245041.62</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1245041.62</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>459724.5478668455</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>4654722</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>4654722.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>67.02000000000001</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>63.32</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>54.65</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>63.32</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>54.65</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>3352293.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>3063130.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>3063130</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>2184802.2</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1152283.22</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1152283.22</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>344715.3285418889</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>3352293</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>3352293.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>66.66</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>62.95</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>54.06</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>54.06</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>3112296.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>2998074.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>2998074</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1928726.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1085599.98</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1085599.98</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>307651.1463440256</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>3112296</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>3112296.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>65.55999999999999</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>62.51</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>53.48</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>53.48</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>2475082.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>2794079.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>2794079.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1676143.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1023637.78</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1023637.78</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>269428.7379776486</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>2475082</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2475082.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>65.24</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>62.24</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>52.98</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>52.98</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1788530.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>2452770.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>2452770.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1786777.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>974413.24</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>974413.24</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>273475.7710979092</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1788530</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1788530.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>63.96</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>61.75</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>52.48</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>52.48</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>4587449.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2160337.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>2160337.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1740334.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>939103.18</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>939103.1800000001</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>343049.398016213</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>4587449</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>4587449.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>62.17999999999999</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>60.82</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>60.82</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>51.93</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>3027013.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1306474.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1306474.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1320421.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>847995.24</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>847995.24</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>130304.3508274965</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>3027013</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>3027013.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>60.98</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>59.82</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>51.4</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>2092324.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>859379.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>859379.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1075640.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>787885.56</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>787885.5600000001</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-11081.30054308032</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>2092324</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>2092324.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>174.8</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>174.25</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>169.68</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>174.25</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>169.68</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>174920.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>330323.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>330323.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>389597.7</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>211843.7</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>211843.7</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>10191.75853036175</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>174920</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>174920.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>177.5</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>174.42</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>169.77</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>174.42</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>169.77</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>163410.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>540797.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>540797.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>388405.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>210395.5</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>210395.5</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>27168.1896322539</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>163410</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>163410.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>179.6</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>175.02</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>170.11</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>175.02</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>170.11</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>203938.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>573351.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>573351.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>391089.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>209730.88</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>209730.88</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>51683.15586237633</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>203938</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>203938.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>181.2</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>175.6</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>170.27</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>175.6</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>170.27</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>335990.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>559007.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>559007.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>378699.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>207102.88</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>207102.88</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>80516.42348175216</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>335990</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>335990.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>181.6</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>175.75</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>170.28</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>175.75</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>170.28</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>773361.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>525593.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>525593.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>360604.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>201294.06</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>201294.06</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>104682.7906707979</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>773361</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>773361.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>181.2</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>175.1</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>170.06</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>175.1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>170.06</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1227288.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>448871.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>448871.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>294742.4</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>186570.02</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>186570.02</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>88606.32270262047</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1227288</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1227288.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>178.8</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>174.2</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>169.75</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>169.75</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>326179.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>236013.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>236013</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>181083.3</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>163556.08</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>163556.08</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>13840.39265155917</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>326179</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>326179.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>176.4</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>173.75</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>169.66</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>173.75</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>169.66</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>132221.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>208827.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>208827</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>155954.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>158247.22</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>158247.22</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>3085.014269630134</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>132221</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>132221.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>173.4</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>172.7</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>169.57</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>169.57</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>168917.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>198391.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>198391.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>148197.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>158796.84</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>158796.84</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>8391.223214387574</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>168917</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>168917.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>171.8</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>171.9</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>169.65</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>171.9</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>169.65</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>389753.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>195615.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>195615.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>134490.8</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>162120.26</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>162120.26</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>11740.12087781297</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>389753</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>389753.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>170.5</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>170.55</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>169.86</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>170.55</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>169.86</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>162995.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>140613.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>140613.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>106093.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>175583.3</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>175583.3</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-7556.029634358332</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>162995</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>162995.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>118.6</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>120.05</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>110.42</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>120.05</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>110.42</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>572706321.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>1111375035.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>1111375035.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>2938471107.8</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>2497141421.7</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>2497141421.7</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-397300976.1281259</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>572706321</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>572706321.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>118.8</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>120.78</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>109.68</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>120.78</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>109.68</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>867429397.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1644014404.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1644014404.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>3026451007.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>2487040729.44</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2487040729.44</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-321917954.0829532</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>867429397</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>867429397.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>119.1</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>121.82</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>108.97</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>121.82</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>108.97</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>819565292.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>2072529213.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>2072529213.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>3109547376.7</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>2471167620.6</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>2471167620.6</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-234308325.229744</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>819565292</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>819565292.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>119.0</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>122.62</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>108.22</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>122.62</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>108.22</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>1442562498.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>2561841839.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>2561841839.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>3133891576.2</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>2455866202.98</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>2455866202.98</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-95655261.14552546</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>1442562498</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>1442562498.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>120.2</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>122.85</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>107.48</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>107.48</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1854611671.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>4105983416.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>4105983416.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>3075297705.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>2428420913.06</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>2428420913.06</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>39087103.37284136</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1854611671</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1854611671.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>122.0</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>122.52</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>106.66</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>122.52</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>106.66</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>3235903165.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>4765567179.8</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>4765567179.8</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>2991524891.3</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>2392460304.48</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>2392460304.48</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>186032101.8857636</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>3235903165</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>3235903165.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>122.2</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>122.3</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>105.89</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>105.89</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>3010003440.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>4408887609.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>4408887609.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>2800902853.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>2329215959.6</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>2329215959.6</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>241314007.4797325</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>3010003440</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>3010003440.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>122.0</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>122.05</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>105.1</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>122.05</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>105.1</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>3266128424.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>4146565540.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>4146565540.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>2669838455.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>2270639675.26</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>2270639675.26</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>335873342.882555</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>3266128424</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>3266128424.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>120.9</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>121.3</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>104.32</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>104.32</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>9163270381.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>3705941312.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>3705941312.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>2548478177.7</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>2206513442.02</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2206513442.02</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>431520668.6407809</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>9163270381</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>9163270381.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>119.5</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>119.99</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>103.43</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>103.43</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>5152530489.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>2044611993.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>2044611993.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>1802145209.3</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2025799608.9</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2025799608.9</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-79088385.26320982</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>5152530489</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>5152530489.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>117.5</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>118.22</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>102.47</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>118.22</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>102.47</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>1452505315.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1217482602.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1217482602.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>1640209239.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>1923833941.42</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>1923833941.42</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-375983174.3666532</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>1452505315</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>1452505315.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
